--- a/files/VitaGen_Financial_Model_Short_DEMO.xlsx
+++ b/files/VitaGen_Financial_Model_Short_DEMO.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B4" s="28" t="inlineStr">
         <is>
-          <t>~1,50 млн чел.</t>
+          <t>1 273 тыс. чел. (2023, Росстат)</t>
         </is>
       </c>
       <c r="C4" s="28" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B5" s="28" t="inlineStr">
         <is>
-          <t>~2,0</t>
+          <t>2,50 (прогноз 2024)</t>
         </is>
       </c>
       <c r="C5" s="28" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B6" s="28" t="inlineStr">
         <is>
-          <t>~20–28% пар</t>
+          <t>≈1 из 13 (ВОЗ, 2025)</t>
         </is>
       </c>
       <c r="C6" s="28" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B7" s="28" t="inlineStr">
         <is>
-          <t>~197–261 тыс.</t>
+          <t>~136–165 тыс.</t>
         </is>
       </c>
       <c r="C7" s="28" t="inlineStr">
@@ -1455,12 +1455,12 @@
       </c>
       <c r="B12" s="28" t="inlineStr">
         <is>
-          <t>~17–61 млрд ₽/год</t>
+          <t>~21–46 млрд ₽/год</t>
         </is>
       </c>
       <c r="C12" s="28" t="inlineStr">
         <is>
-          <t>Расчёт: ~156 тыс. циклов × ~310 тыс. ₽ средневзвешенно (ОМС+коммерция)</t>
+          <t>Расчёт: ~141 тыс. циклов × ~310 тыс. ₽ средневзвешенно (ОМС+коммерция)</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B13" s="28" t="inlineStr">
         <is>
-          <t>~3–7 млрд ₽/год</t>
+          <t>~1,8–3 млрд ₽/год</t>
         </is>
       </c>
       <c r="C13" s="28" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
-          <t>Расчёт модели; ~13–20% SAM РФ + ранний APAC</t>
+          <t>Расчёт модели; ~12–17% SAM РФ + ранний APAC</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B15" s="28" t="inlineStr">
         <is>
-          <t>~562–1166 тыс.</t>
+          <t>крупнейший рынок</t>
         </is>
       </c>
       <c r="C15" s="28" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="B18" s="28" t="inlineStr">
         <is>
-          <t>~$0,7–3,0 млрд (2025), CAGR 12–17%</t>
+          <t>отраслевые оценки: рост двузначный (требуют подтверждения)</t>
         </is>
       </c>
       <c r="C18" s="28" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17–61 млрд ₽/год</t>
+          <t>21–46 млрд ₽/год</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3–7 млрд ₽/год</t>
+          <t>1,8–3 млрд ₽/год</t>
         </is>
       </c>
     </row>
